--- a/data/raw/양산평가_샘플.xlsx
+++ b/data/raw/양산평가_샘플.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
   <si>
     <t xml:space="preserve">평가일</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
@@ -281,7 +284,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="h:mm"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,11 +320,6 @@
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="3">
@@ -387,24 +385,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -663,446 +665,502 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2"/>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2"/>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="n">
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>46191</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2"/>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>46191</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="n">
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>46191</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="n">
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2"/>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="A17" s="4" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="A19" s="4" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="A20" s="4" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="A21" s="4" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="A22" s="4" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="A23" s="4" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1123,354 +1181,354 @@
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>0.383333333333333</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="N2" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>0.445138888888889</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="I3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="K3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>0.545138888888889</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.401388888888889</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.598611111111111</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.490972222222222</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="K7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>0.401388888888889</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="M7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.63125</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="K8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0.598611111111111</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0.490972222222222</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.63125</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="2" t="s">
+      <c r="L8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>82</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
